--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -646,7 +646,7 @@
     <t>火麟剑诀</t>
   </si>
   <si>
-    <t>增加5%物攻增幅</t>
+    <t>增加5%物攻倍率</t>
   </si>
   <si>
     <t>·吸血</t>
@@ -739,7 +739,7 @@
     <t>·魔体</t>
   </si>
   <si>
-    <t>增加{0}%魔法增幅</t>
+    <t>增加{0}%魔法倍率</t>
   </si>
   <si>
     <t>·汲取</t>
@@ -829,7 +829,7 @@
     <t>·神体</t>
   </si>
   <si>
-    <t>增加{0}%道术增幅</t>
+    <t>增加{0}%道术倍率</t>
   </si>
   <si>
     <t>·回复</t>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="AA14" s="1">
-        <v>2004</v>
+        <v>10004</v>
       </c>
       <c r="AB14" s="1">
         <v>5</v>
@@ -4170,6 +4170,12 @@
       <c r="X36" s="1">
         <v>0</v>
       </c>
+      <c r="AA36" s="1">
+        <v>10005</v>
+      </c>
+      <c r="AB36" s="1">
+        <v>5</v>
+      </c>
       <c r="AG36" s="1">
         <v>1</v>
       </c>
@@ -5528,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="AA60" s="1">
-        <v>2006</v>
+        <v>10006</v>
       </c>
       <c r="AB60" s="1">
         <v>5</v>
